--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_46.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4115958.767684798</v>
+        <v>4152316.813992016</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117056482</v>
+        <v>603.5370117053528</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117056482</v>
+        <v>603.5370117053528</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>260.6752387688036</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
@@ -799,10 +799,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>156.3490875886176</v>
       </c>
     </row>
     <row r="4">
@@ -909,7 +909,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
         <v>184.8805867536895</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>5.361097301488838</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>274.3712345074512</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1146,10 +1146,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>135.4247273329228</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -1219,16 +1219,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>150.4346265429118</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.83504507946625</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>200.5295027796756</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
@@ -1459,7 +1459,7 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>177.5914272286986</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
         <v>4.021973978873973</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T12" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1513,7 +1513,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1574,7 +1574,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>3.99961134672543</v>
@@ -1744,13 +1744,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>284.9649587918013</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -1930,7 +1930,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1987,7 +1987,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>251.9832086481071</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2039,7 +2039,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C21" t="n">
-        <v>213.6917283274922</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -2285,7 +2285,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090244326</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2331,10 +2331,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2395,16 +2395,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
         <v>3.999611346725456</v>
@@ -2449,16 +2449,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>272.4545553273606</v>
+        <v>272.4545553273607</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2522,7 +2522,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090244517</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
@@ -2638,19 +2638,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>195.2639131038853</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H27" t="n">
         <v>325.021973978874</v>
       </c>
       <c r="I27" t="n">
-        <v>173.5918158819729</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2680,13 +2680,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2747,19 +2747,19 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O28" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2799,16 +2799,16 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>84.35021607332619</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2869,22 +2869,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>353.9253867592582</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N31" t="n">
         <v>155.2579933044718</v>
@@ -2987,13 +2987,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3036,16 +3036,16 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>84.35021607332619</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3106,25 +3106,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>324.9996113467254</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,19 +3148,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>404.6459244566753</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M34" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N34" t="n">
         <v>155.2579933044718</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,10 +3276,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>21.67209722191262</v>
@@ -3355,10 +3355,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592579</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T36" t="n">
-        <v>254.9671660051473</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
@@ -3406,7 +3406,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N37" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474549048</v>
       </c>
       <c r="O37" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>113.5995101105026</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>3.999611346725456</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>180.333570877285</v>
@@ -3640,13 +3640,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273604</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3707,7 +3707,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090247624</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
@@ -3826,16 +3826,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>177.5914272286987</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I42" t="n">
-        <v>173.5918158819728</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3865,13 +3865,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N43" t="n">
         <v>155.2579933044718</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090251394</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H44" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,19 +4051,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>3.999611346725456</v>
@@ -4105,7 +4105,7 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
-        <v>254.9671660051473</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
         <v>79.16168051490372</v>
@@ -4117,10 +4117,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4324,28 +4324,28 @@
         <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>834.5019149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>1204.761914974874</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O2" t="n">
-        <v>1204.761914974874</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P2" t="n">
-        <v>1262.853806841132</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S2" t="n">
         <v>1407.815317606417</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358.7282218672851</v>
+        <v>918.0594304751146</v>
       </c>
       <c r="C3" t="n">
-        <v>358.7282218672851</v>
+        <v>918.0594304751146</v>
       </c>
       <c r="D3" t="n">
-        <v>358.7282218672851</v>
+        <v>918.0594304751146</v>
       </c>
       <c r="E3" t="n">
-        <v>358.7282218672851</v>
+        <v>918.0594304751146</v>
       </c>
       <c r="F3" t="n">
-        <v>358.7282218672851</v>
+        <v>574.9925190227137</v>
       </c>
       <c r="G3" t="n">
-        <v>29.92</v>
+        <v>574.9925190227137</v>
       </c>
       <c r="H3" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I3" t="n">
         <v>29.92</v>
@@ -4421,31 +4421,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R3" t="n">
-        <v>1229.477708379845</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S3" t="n">
-        <v>1166.357696980486</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T3" t="n">
-        <v>1161.839066209984</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U3" t="n">
-        <v>1161.641161363597</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V3" t="n">
-        <v>1146.983921776203</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W3" t="n">
-        <v>1114.283777422841</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X3" t="n">
-        <v>736.505999645063</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y3" t="n">
-        <v>358.7282218672851</v>
+        <v>918.0594304751146</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>654.5935815663379</v>
+        <v>253.0866383453244</v>
       </c>
       <c r="C4" t="n">
-        <v>654.5935815663379</v>
+        <v>379.0886441637601</v>
       </c>
       <c r="D4" t="n">
-        <v>654.5935815663379</v>
+        <v>492.4077882887602</v>
       </c>
       <c r="E4" t="n">
-        <v>654.5935815663379</v>
+        <v>610.2366925001733</v>
       </c>
       <c r="F4" t="n">
-        <v>654.5935815663379</v>
+        <v>734.5976650921087</v>
       </c>
       <c r="G4" t="n">
-        <v>654.5935815663379</v>
+        <v>888.1863260609612</v>
       </c>
       <c r="H4" t="n">
-        <v>654.5935815663379</v>
+        <v>1059.321902040031</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>505.7585226289696</v>
+        <v>29.92</v>
       </c>
       <c r="V4" t="n">
-        <v>654.5935815663379</v>
+        <v>29.92</v>
       </c>
       <c r="W4" t="n">
-        <v>654.5935815663379</v>
+        <v>29.92</v>
       </c>
       <c r="X4" t="n">
-        <v>654.5935815663379</v>
+        <v>29.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>654.5935815663379</v>
+        <v>141.3293006790323</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K5" t="n">
         <v>400.18</v>
       </c>
-      <c r="K5" t="n">
-        <v>770.4399999999999</v>
-      </c>
       <c r="L5" t="n">
-        <v>1067.648108133742</v>
+        <v>464.2419149748744</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>834.5019149748744</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1204.761914974874</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1204.761914974874</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1262.853806841132</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="D6" t="n">
-        <v>241.6095073802453</v>
+        <v>724.5355927891701</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>378.4021612518846</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>35.33524979948368</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>35.33524979948368</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>35.33524979948368</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4661,28 +4661,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1069.104450824218</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>691.3266730464404</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>686.8080422759385</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>309.0302644981606</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>294.3730249107666</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W6" t="n">
-        <v>261.6728805574044</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="7">
@@ -4692,16 +4692,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>700.1293446184156</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="C7" t="n">
-        <v>700.1293446184156</v>
+        <v>344.620323690067</v>
       </c>
       <c r="D7" t="n">
-        <v>700.1293446184156</v>
+        <v>457.9394678150671</v>
       </c>
       <c r="E7" t="n">
-        <v>700.1293446184156</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="F7" t="n">
         <v>700.1293446184156</v>
@@ -4746,22 +4746,22 @@
         <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>238.8678600292439</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>238.8678600292439</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="V7" t="n">
-        <v>437.6892529151899</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="W7" t="n">
-        <v>437.6892529151899</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="X7" t="n">
-        <v>588.7200439393833</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="Y7" t="n">
-        <v>700.1293446184156</v>
+        <v>259.1973975316665</v>
       </c>
     </row>
     <row r="8">
@@ -4789,7 +4789,7 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4798,22 +4798,22 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>1140.7</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M8" t="n">
-        <v>1140.7</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N8" t="n">
-        <v>1140.7</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O8" t="n">
-        <v>1140.7</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="C9" t="n">
-        <v>939.1951479051093</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="D9" t="n">
-        <v>587.7429389175309</v>
+        <v>871.07451121485</v>
       </c>
       <c r="E9" t="n">
-        <v>241.6095073802453</v>
+        <v>524.9410796775644</v>
       </c>
       <c r="F9" t="n">
-        <v>241.6095073802453</v>
+        <v>181.8741682251635</v>
       </c>
       <c r="G9" t="n">
-        <v>241.6095073802453</v>
+        <v>181.8741682251635</v>
       </c>
       <c r="H9" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1143.60646374105</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>1143.408558894664</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V9" t="n">
-        <v>1128.75131930727</v>
+        <v>1275.29023773295</v>
       </c>
       <c r="W9" t="n">
-        <v>1096.051174953908</v>
+        <v>1242.590093379587</v>
       </c>
       <c r="X9" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="Y9" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>631.7468391594613</v>
+        <v>737.7426096864748</v>
       </c>
       <c r="C10" t="n">
-        <v>631.7468391594613</v>
+        <v>863.7446155049106</v>
       </c>
       <c r="D10" t="n">
-        <v>745.0659832844614</v>
+        <v>977.0637596299107</v>
       </c>
       <c r="E10" t="n">
-        <v>862.8948874958744</v>
+        <v>1094.892663841324</v>
       </c>
       <c r="F10" t="n">
-        <v>862.8948874958744</v>
+        <v>1094.892663841324</v>
       </c>
       <c r="G10" t="n">
-        <v>1016.483548464727</v>
+        <v>1094.892663841324</v>
       </c>
       <c r="H10" t="n">
-        <v>1016.483548464727</v>
+        <v>1266.028239820393</v>
       </c>
       <c r="I10" t="n">
-        <v>1016.483548464727</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V10" t="n">
-        <v>458.0187904176125</v>
+        <v>475.302517983249</v>
       </c>
       <c r="W10" t="n">
-        <v>519.9895014931692</v>
+        <v>475.302517983249</v>
       </c>
       <c r="X10" t="n">
-        <v>519.9895014931692</v>
+        <v>626.3333090074425</v>
       </c>
       <c r="Y10" t="n">
-        <v>519.9895014931692</v>
+        <v>737.7426096864748</v>
       </c>
     </row>
     <row r="11">
@@ -5023,34 +5023,34 @@
         <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>1844.448527309012</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
-        <v>1844.448527309012</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N11" t="n">
-        <v>1844.448527309012</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>2005.578628691967</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
-        <v>2202.170635030587</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>668.0405455662465</v>
+        <v>343.798121323822</v>
       </c>
       <c r="C12" t="n">
-        <v>627.5355835000654</v>
+        <v>303.2931592576409</v>
       </c>
       <c r="D12" t="n">
-        <v>276.083374512487</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E12" t="n">
-        <v>254.1923672176257</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F12" t="n">
-        <v>235.3678800076491</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
         <v>55.98259997866058</v>
@@ -5135,28 +5135,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
         <v>1604.638050209959</v>
       </c>
       <c r="T12" t="n">
-        <v>1522.440726853217</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U12" t="n">
-        <v>1442.479433403819</v>
+        <v>793.9945849189708</v>
       </c>
       <c r="V12" t="n">
-        <v>1348.024214018445</v>
+        <v>699.5393655335969</v>
       </c>
       <c r="W12" t="n">
-        <v>1235.526089867104</v>
+        <v>587.041241382255</v>
       </c>
       <c r="X12" t="n">
-        <v>1135.664736891965</v>
+        <v>487.179888407116</v>
       </c>
       <c r="Y12" t="n">
-        <v>732.239087633243</v>
+        <v>407.9966633908186</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O13" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P13" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R13" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5269,16 +5269,16 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L14" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M14" t="n">
-        <v>1009.32297330616</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N14" t="n">
         <v>1651.83297330616</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F15" t="n">
         <v>60.0226114399994</v>
@@ -5387,13 +5387,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>960.3194683243149</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y15" t="n">
-        <v>556.8938190655933</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="16">
@@ -5506,25 +5506,25 @@
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L17" t="n">
-        <v>1418.446838088717</v>
+        <v>1376.091327711023</v>
       </c>
       <c r="M17" t="n">
-        <v>2060.956838088718</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N17" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O17" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>816.9377012410212</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C18" t="n">
-        <v>452.1903149324157</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D18" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E18" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5630,7 +5630,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y18" t="n">
-        <v>1205.378667550442</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="19">
@@ -5682,13 +5682,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C20" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D20" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E20" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F20" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G20" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M20" t="n">
-        <v>1592.143276253736</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N20" t="n">
-        <v>2234.653276253736</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O20" t="n">
-        <v>2395.783377636692</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
-        <v>2592.375383975311</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="21">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1316.525394051095</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.675163417264</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D21" t="n">
         <v>749.2229544296858</v>
@@ -5901,31 +5901,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J22" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611872</v>
       </c>
       <c r="K22" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.08070002415</v>
       </c>
       <c r="L22" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405761</v>
       </c>
       <c r="M22" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468593</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605491</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111702</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645261</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881645</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741744</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5974,28 +5974,28 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L23" t="n">
-        <v>1418.446838088717</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M23" t="n">
-        <v>1418.446838088717</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N23" t="n">
-        <v>1418.446838088717</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
         <v>2596</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1141.180125483445</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C24" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D24" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F24" t="n">
         <v>60.02261143999941</v>
@@ -6092,19 +6092,19 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V24" t="n">
-        <v>1672.26663826087</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W24" t="n">
-        <v>1559.768514109528</v>
+        <v>587.0412413822551</v>
       </c>
       <c r="X24" t="n">
-        <v>1284.561892566739</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y24" t="n">
-        <v>1205.378667550442</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="25">
@@ -6126,43 +6126,43 @@
         <v>809.1641510572457</v>
       </c>
       <c r="F25" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236491879</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141262371</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187274</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434832</v>
       </c>
       <c r="J25" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611874</v>
       </c>
       <c r="K25" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024152</v>
       </c>
       <c r="L25" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405763</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468595</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605493</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111704</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645281</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881665</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741937</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6205,7 +6205,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G26" t="n">
         <v>125.5027119537179</v>
@@ -6220,22 +6220,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L26" t="n">
-        <v>1418.446838088717</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M26" t="n">
-        <v>2060.956838088718</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.277892278425</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O26" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P26" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
@@ -6278,19 +6278,19 @@
         <v>1276.020431984914</v>
       </c>
       <c r="D27" t="n">
-        <v>1248.81064723976</v>
+        <v>1248.810647239759</v>
       </c>
       <c r="E27" t="n">
-        <v>902.6772157024741</v>
+        <v>1051.574371377249</v>
       </c>
       <c r="F27" t="n">
-        <v>559.6103042500731</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G27" t="n">
-        <v>555.5702927887343</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H27" t="n">
-        <v>227.2652685676494</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6326,7 +6326,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U27" t="n">
         <v>1766.721857646244</v>
@@ -6341,7 +6341,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y27" t="n">
-        <v>1380.723936118092</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="28">
@@ -6390,16 +6390,16 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C29" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D29" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
@@ -6457,13 +6457,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.599638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N29" t="n">
         <v>1651.83297330616</v>
@@ -6490,16 +6490,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W29" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>492.6952769985969</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C30" t="n">
-        <v>452.1903149324158</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872616</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
         <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6557,28 +6557,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1886.686949702618</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1429.292781642309</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1347.095458285567</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>942.8917405937456</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>848.4365212083717</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>556.8938190655934</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="31">
@@ -6621,19 +6621,19 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D32" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G32" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H32" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>991.9887866314309</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>1634.498786631431</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N32" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O32" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6727,16 +6727,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W32" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1010.52448325439</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C33" t="n">
-        <v>970.0195211882091</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D33" t="n">
-        <v>942.8097364430549</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E33" t="n">
-        <v>920.9187291481937</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
-        <v>577.8518176957928</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G33" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H33" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I33" t="n">
         <v>51.92</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>1756.031307473563</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S33" t="n">
-        <v>1622.879563655678</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1540.682240298937</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U33" t="n">
-        <v>1460.720946849539</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V33" t="n">
-        <v>1366.265727464165</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W33" t="n">
-        <v>1253.767603312823</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>1153.906250337684</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
-        <v>1074.723025321387</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="34">
@@ -6858,22 +6858,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N34" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H35" t="n">
         <v>51.92</v>
@@ -6928,52 +6928,52 @@
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N35" t="n">
-        <v>2234.653276253736</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O35" t="n">
-        <v>2395.783377636692</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P35" t="n">
-        <v>2592.375383975311</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="36">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>492.6952769985969</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C36" t="n">
-        <v>452.1903149324158</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D36" t="n">
         <v>424.9805301872616</v>
@@ -6995,10 +6995,10 @@
         <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7031,10 +7031,10 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S36" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T36" t="n">
         <v>1671.337882527992</v>
@@ -7049,10 +7049,10 @@
         <v>1384.423245541878</v>
       </c>
       <c r="X36" t="n">
-        <v>960.3194683243152</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y36" t="n">
-        <v>881.1362433080178</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="37">
@@ -7062,55 +7062,55 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>686.6440969023969</v>
+        <v>686.6440969024278</v>
       </c>
       <c r="C37" t="n">
-        <v>734.4361027208327</v>
+        <v>734.4361027208636</v>
       </c>
       <c r="D37" t="n">
-        <v>769.5452468458327</v>
+        <v>769.5452468458636</v>
       </c>
       <c r="E37" t="n">
-        <v>809.1641510572457</v>
+        <v>809.1641510572766</v>
       </c>
       <c r="F37" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236492121</v>
       </c>
       <c r="G37" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141262613</v>
       </c>
       <c r="H37" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187298</v>
       </c>
       <c r="I37" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.283805434857</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611898</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024176</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405787</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468619</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7128,10 +7128,10 @@
         <v>547.0766675328789</v>
       </c>
       <c r="X37" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8974585571034</v>
       </c>
       <c r="Y37" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0967592361357</v>
       </c>
     </row>
     <row r="38">
@@ -7171,19 +7171,19 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L38" t="n">
-        <v>950.0896384907273</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.599638490728</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N38" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O38" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P38" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>912.8601939406431</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C39" t="n">
-        <v>548.1128076320376</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D39" t="n">
-        <v>520.9030228868835</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E39" t="n">
-        <v>174.769591349598</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
         <v>60.02261143999941</v>
@@ -7265,31 +7265,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q39" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R39" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U39" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1156.103313999076</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>1056.241961023937</v>
+        <v>1284.56189256674</v>
       </c>
       <c r="Y39" t="n">
-        <v>977.0587360076396</v>
+        <v>881.1362433080178</v>
       </c>
     </row>
     <row r="40">
@@ -7323,31 +7323,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611905</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024183</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405794</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468627</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605524</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111735</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645594</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881978</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949745075</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
@@ -7408,46 +7408,46 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L41" t="n">
-        <v>950.0896384907273</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.599638490728</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N41" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P41" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1316.525394051095</v>
+        <v>992.2829698086707</v>
       </c>
       <c r="C42" t="n">
-        <v>951.7780077424893</v>
+        <v>951.7780077424896</v>
       </c>
       <c r="D42" t="n">
-        <v>924.5682229973352</v>
+        <v>924.5682229973355</v>
       </c>
       <c r="E42" t="n">
-        <v>578.4347914600496</v>
+        <v>578.4347914600501</v>
       </c>
       <c r="F42" t="n">
-        <v>235.3678800076487</v>
+        <v>559.6103042500735</v>
       </c>
       <c r="G42" t="n">
-        <v>231.3278685463099</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H42" t="n">
-        <v>227.2652685676493</v>
+        <v>51.92</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7511,7 +7511,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U42" t="n">
         <v>1766.721857646244</v>
@@ -7526,7 +7526,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y42" t="n">
-        <v>1380.723936118091</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="43">
@@ -7536,55 +7536,55 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>686.6440969024729</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C43" t="n">
-        <v>734.4361027209087</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D43" t="n">
-        <v>769.5452468459088</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E43" t="n">
-        <v>809.1641510573218</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236492572</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G43" t="n">
-        <v>931.1258141263064</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.892525187343</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I43" t="n">
-        <v>1189.283805434902</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J43" t="n">
-        <v>1515.576154611943</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024222</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L43" t="n">
-        <v>1608.654647405832</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468665</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605562</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111773</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645975</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425882359</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949748884</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7596,16 +7596,16 @@
         <v>332.7843563872555</v>
       </c>
       <c r="V43" t="n">
-        <v>453.3957492732775</v>
+        <v>453.3957492732014</v>
       </c>
       <c r="W43" t="n">
-        <v>547.076667532955</v>
+        <v>547.0766675328789</v>
       </c>
       <c r="X43" t="n">
-        <v>619.8974585571485</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y43" t="n">
-        <v>653.0967592361808</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C44" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D44" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E44" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G44" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H44" t="n">
         <v>51.92</v>
@@ -7639,52 +7639,52 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>793.271024763446</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M44" t="n">
-        <v>1592.599638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N44" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P44" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W44" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="45">
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C45" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E45" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F45" t="n">
         <v>60.02261143999941</v>
@@ -7748,22 +7748,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U45" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>960.3194683243149</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y45" t="n">
-        <v>556.8938190655933</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="46">
@@ -7967,7 +7967,7 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>364.0430754681111</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,16 +8201,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
         <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
-        <v>235.5012052109776</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
         <v>778.0826666125488</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>364.0430754681111</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,25 +8441,25 @@
         <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748744</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
-        <v>300.2102102361029</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>301.434429149855</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>421.2909076101267</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>361.7270524351312</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>430.7657085427136</v>
+        <v>430.7657085427137</v>
       </c>
       <c r="M17" t="n">
-        <v>950.4344291498551</v>
+        <v>579.9613438924174</v>
       </c>
       <c r="N17" t="n">
-        <v>409.6042294964216</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,16 +9386,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N20" t="n">
         <v>879.4920535472222</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27.14469655484982</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L23" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M23" t="n">
-        <v>301.434429149855</v>
+        <v>699.241868512898</v>
       </c>
       <c r="N23" t="n">
         <v>230.4920535472222</v>
       </c>
       <c r="O23" t="n">
-        <v>377.6899601296239</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>23.48346824708341</v>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>430.7657085427136</v>
@@ -9872,7 +9872,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M29" t="n">
-        <v>950.4344291498551</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N29" t="n">
-        <v>290.3237048759414</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10346,7 +10346,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>840.3699380391354</v>
+        <v>290.7846768324985</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M35" t="n">
         <v>950.4344291498551</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27.14469655484982</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,10 +10814,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N38" t="n">
         <v>879.4920535472222</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11051,10 +11051,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>950.4344291498551</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N41" t="n">
         <v>879.4920535472222</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>60.29262328527625</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495925071</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495905887</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24605,7 +24605,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24836,7 +24836,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24848,7 +24848,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25313,7 +25313,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.8382458495670164</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495595273</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25784,7 +25784,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495218259</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6118098.971733757</v>
+        <v>6118098.971733758</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6873713.125193076</v>
+        <v>6873713.125193077</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7629327.278652395</v>
+        <v>7629327.278652396</v>
       </c>
     </row>
     <row r="12">
@@ -26269,28 +26269,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382485</v>
       </c>
       <c r="C2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382485</v>
       </c>
       <c r="D2" t="n">
         <v>1448283.596382485</v>
       </c>
       <c r="E2" t="n">
-        <v>1448260.460797036</v>
+        <v>1448260.460797035</v>
       </c>
       <c r="F2" t="n">
         <v>1448260.460797035</v>
       </c>
       <c r="G2" t="n">
-        <v>1448260.460797035</v>
+        <v>1448260.460797036</v>
       </c>
       <c r="H2" t="n">
         <v>1448260.460797035</v>
       </c>
       <c r="I2" t="n">
-        <v>1448260.460797034</v>
+        <v>1448260.460797036</v>
       </c>
       <c r="J2" t="n">
         <v>1448260.460797035</v>
@@ -26302,13 +26302,13 @@
         <v>1448260.460797035</v>
       </c>
       <c r="M2" t="n">
+        <v>1448260.460797036</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1448260.460797036</v>
+      </c>
+      <c r="O2" t="n">
         <v>1448260.460797035</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1448260.460797035</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1448260.460797037</v>
       </c>
       <c r="P2" t="n">
         <v>1448260.460797035</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667653</v>
+        <v>570963.5697337883</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159823</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005103</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193655</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286018</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604943</v>
+        <v>466508.6099301391</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>581130.261715719</v>
+        <v>587631.6266486963</v>
       </c>
       <c r="C6" t="n">
-        <v>814237.1839032072</v>
+        <v>820738.548836185</v>
       </c>
       <c r="D6" t="n">
-        <v>816248.831319032</v>
+        <v>822750.1962520088</v>
       </c>
       <c r="E6" t="n">
-        <v>294826.9320008609</v>
+        <v>301289.9231312142</v>
       </c>
       <c r="F6" t="n">
-        <v>886062.9948190828</v>
+        <v>892525.985949437</v>
       </c>
       <c r="G6" t="n">
-        <v>887751.384340736</v>
+        <v>894214.3754710908</v>
       </c>
       <c r="H6" t="n">
-        <v>889442.1172506987</v>
+        <v>895905.1083810531</v>
       </c>
       <c r="I6" t="n">
-        <v>891135.2104512453</v>
+        <v>897598.2015816008</v>
       </c>
       <c r="J6" t="n">
-        <v>504382.6810661702</v>
+        <v>510845.6721965248</v>
       </c>
       <c r="K6" t="n">
-        <v>894528.5464450042</v>
+        <v>900991.5375753584</v>
       </c>
       <c r="L6" t="n">
-        <v>896228.8241673483</v>
+        <v>902691.8152977022</v>
       </c>
       <c r="M6" t="n">
-        <v>801131.5320473156</v>
+        <v>807594.5231776705</v>
       </c>
       <c r="N6" t="n">
-        <v>899636.6881380792</v>
+        <v>906099.6792684341</v>
       </c>
       <c r="O6" t="n">
-        <v>644544.3107365429</v>
+        <v>651007.3018668961</v>
       </c>
       <c r="P6" t="n">
-        <v>903054.418388125</v>
+        <v>909517.4095184793</v>
       </c>
     </row>
   </sheetData>
@@ -27002,13 +27002,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>272.9767472028209</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27578,10 +27578,10 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>243.0423051775168</v>
       </c>
     </row>
     <row r="4">
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>368.9819193021434</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>349.5087535872954</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I5" t="n">
         <v>134.2726973711268</v>
@@ -27721,7 +27721,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27770,7 +27770,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>204.211515004954</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,16 +27797,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>259.2807514641734</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27831,16 +27831,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>359.011030646429</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>379.4651136339165</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>225.6751851125965</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -27998,16 +27998,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>179.6145549831319</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C10" t="n">
         <v>400</v>
-      </c>
-      <c r="C10" t="n">
-        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28080,16 +28080,16 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
+        <v>244.8599384153005</v>
+      </c>
+      <c r="H10" t="n">
         <v>400</v>
       </c>
-      <c r="H10" t="n">
-        <v>227.1357818393235</v>
-      </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>293.0367009803493</v>
       </c>
       <c r="J10" t="n">
-        <v>396.2647849014816</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
         <v>267.1509377355693</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.1680042930194</v>
+      </c>
+      <c r="T10" t="n">
+        <v>209.2386648669134</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
-      </c>
-      <c r="T10" t="n">
-        <v>400</v>
-      </c>
-      <c r="U10" t="n">
-        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>288.9694876928074</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28159,13 +28159,13 @@
         <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="H11" t="n">
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28229,7 +28229,7 @@
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.408184118027</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
@@ -28238,7 +28238,7 @@
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28271,16 +28271,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
@@ -28292,7 +28292,7 @@
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28523,13 +28523,13 @@
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -28709,7 +28709,7 @@
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28766,7 +28766,7 @@
         <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>147.4081841180273</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,13 +28934,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C21" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>321</v>
+        <v>321.0000000000049</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29110,10 +29110,10 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29174,16 +29174,16 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,16 +29228,16 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>147.4081841180269</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29262,7 +29262,7 @@
         <v>321</v>
       </c>
       <c r="F25" t="n">
-        <v>321</v>
+        <v>321.0000000000068</v>
       </c>
       <c r="G25" t="n">
         <v>321</v>
@@ -29417,19 +29417,19 @@
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>147.4081841180273</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>18.05909831126246</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29578,7 +29578,7 @@
         <v>321</v>
       </c>
       <c r="F29" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="G29" t="n">
         <v>321</v>
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29648,13 +29648,13 @@
         <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -29693,16 +29693,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T30" t="n">
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V30" t="n">
         <v>321</v>
@@ -29815,7 +29815,7 @@
         <v>321</v>
       </c>
       <c r="F32" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="G32" t="n">
         <v>321</v>
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29885,25 +29885,25 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,10 +29927,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>96.68764642060961</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -30058,7 +30058,7 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I35" t="n">
         <v>96.76634561233286</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>321</v>
@@ -30167,13 +30167,13 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="S36" t="n">
         <v>321</v>
       </c>
       <c r="T36" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
@@ -30185,7 +30185,7 @@
         <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30264,7 +30264,7 @@
         <v>321</v>
       </c>
       <c r="X37" t="n">
-        <v>321</v>
+        <v>321.0000000000313</v>
       </c>
       <c r="Y37" t="n">
         <v>321</v>
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D39" t="n">
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>226.0367322273743</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
         <v>321</v>
@@ -30419,13 +30419,13 @@
         <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>321</v>
       </c>
       <c r="J40" t="n">
-        <v>321</v>
+        <v>321.0000000000386</v>
       </c>
       <c r="K40" t="n">
         <v>321</v>
@@ -30535,7 +30535,7 @@
         <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,10 +30593,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
@@ -30605,16 +30605,16 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="H42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>18.05909831126257</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>321</v>
       </c>
       <c r="V43" t="n">
-        <v>321.0000000000769</v>
+        <v>321</v>
       </c>
       <c r="W43" t="n">
         <v>321</v>
@@ -30769,7 +30769,7 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I44" t="n">
         <v>96.76634561233286</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,19 +30830,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30884,7 +30884,7 @@
         <v>321</v>
       </c>
       <c r="T45" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="U45" t="n">
         <v>321</v>
@@ -30896,10 +30896,10 @@
         <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46">
@@ -34746,10 +34746,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34758,13 +34758,13 @@
         <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>235.5012052109774</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>197.8798735180906</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>150.3384433710791</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,16 +34980,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
-        <v>373.9999999999999</v>
-      </c>
       <c r="L5" t="n">
-        <v>300.2102102361032</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
         <v>374</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>235.5012052109774</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,16 +35117,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>86.28578399838436</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>155.1400615846995</v>
@@ -35168,22 +35168,22 @@
         <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
-        <v>170.2264487670031</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35220,25 +35220,25 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>373.9999999999999</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
+        <v>64.70900502512563</v>
+      </c>
+      <c r="M8" t="n">
         <v>374</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>358.8888888888889</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35366,16 +35366,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>121.9346551962966</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>62.5966778540977</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
         <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35475,7 +35475,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>397.8074393630433</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>60.29262328527617</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>278.5269147425624</v>
       </c>
       <c r="N17" t="n">
-        <v>179.1121759491994</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,16 +36165,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N20" t="n">
         <v>649</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.661228307766413</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J22" t="n">
-        <v>329.5882314919611</v>
+        <v>329.588231491966</v>
       </c>
       <c r="K22" t="n">
         <v>104.5500458709881</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>649</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>397.807439363043</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>540.4476382942248</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36548,7 +36548,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F25" t="n">
-        <v>46.61714403225807</v>
+        <v>46.61714403226485</v>
       </c>
       <c r="G25" t="n">
         <v>76.57645502732242</v>
@@ -36642,7 +36642,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L26" t="n">
         <v>649</v>
@@ -36651,7 +36651,7 @@
         <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>179.1121759491994</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36660,7 +36660,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36879,16 +36879,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L29" t="n">
         <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>649</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N29" t="n">
-        <v>59.83165132871924</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L32" t="n">
         <v>218.2342914572864</v>
@@ -37125,7 +37125,7 @@
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>609.8778844919133</v>
+        <v>60.29262328527629</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37350,13 +37350,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>179.1121759491997</v>
       </c>
       <c r="L35" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M35" t="n">
         <v>649</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.661228307766413</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37550,7 +37550,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X37" t="n">
-        <v>73.55635456989245</v>
+        <v>73.55635456992378</v>
       </c>
       <c r="Y37" t="n">
         <v>33.53464715053764</v>
@@ -37593,10 +37593,10 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>490.597359871433</v>
       </c>
       <c r="N38" t="n">
         <v>649</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J40" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314919997</v>
       </c>
       <c r="K40" t="n">
         <v>104.5500458709881</v>
@@ -37830,10 +37830,10 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L41" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
-        <v>649</v>
+        <v>490.597359871433</v>
       </c>
       <c r="N41" t="n">
         <v>649</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38018,7 +38018,7 @@
         <v>170.0754447911158</v>
       </c>
       <c r="V43" t="n">
-        <v>121.8296897838607</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W43" t="n">
         <v>94.62719016129032</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>236.2045428832662</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
